--- a/applications.xlsx
+++ b/applications.xlsx
@@ -471,7 +471,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>hr@acme.com</t>
+          <t>elmbarkinidhal@gmail.com</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -479,8 +479,6 @@
           <t>Python; FastAPI; AWS</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -508,8 +506,6 @@
           <t>ML; Python; SQL</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -537,8 +533,6 @@
           <t>Kubernetes; Terraform; CI/CD</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
